--- a/data/credit_bond_2026-09-07.xlsx
+++ b/data/credit_bond_2026-09-07.xlsx
@@ -700,7 +700,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>102683544.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -739,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.6700</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -924,7 +928,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102683543.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2+2</t>
@@ -963,7 +971,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.4800</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-07.xlsx
+++ b/data/credit_bond_2026-09-07.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.20 ~ 2.90</t>
@@ -743,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/2.6700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -753,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 22.82</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -941,7 +943,9 @@
       <c r="E4" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>5.3</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2.05 ~ 2.75</t>
@@ -981,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 22.82</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-07.xlsx
+++ b/data/credit_bond_2026-09-07.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-09" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005B</t>
+          <t>26金融街MTN005B(取消发行)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>102683544.IB</t>
+          <t>DY102683544.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -713,9 +713,7 @@
       <c r="E3" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.20 ~ 2.90</t>
@@ -755,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 22.25</t>
+          <t>C- 21.60</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -833,7 +831,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据(品种二)</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -894,7 +892,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
@@ -922,7 +920,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005A</t>
+          <t>26金融街MTN005</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -944,15 +942,19 @@
         <v>5.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5.3</v>
+        <v>10.3</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2.05 ~ 2.75</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>124.19</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.55</t>
@@ -985,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 22.25</t>
+          <t>C- 21.60</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1063,7 +1065,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据(品种一)</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-07.xlsx
+++ b/data/credit_bond_2026-09-07.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-09" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-10" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 21.60</t>
+          <t>C- 22.43</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 21.60</t>
+          <t>C- 22.43</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1010,7 +1010,9 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.8641</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-09-07.xlsx
+++ b/data/credit_bond_2026-09-07.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-10" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-11" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 22.43</t>
+          <t>C- 24.87</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 22.43</t>
+          <t>C- 24.87</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
